--- a/SBM-corps-FHIR/ig/StructureDefinition-fr-observation-statut.xlsx
+++ b/SBM-corps-FHIR/ig/StructureDefinition-fr-observation-statut.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4369" uniqueCount="631">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4369" uniqueCount="632">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-09-03T12:41:15+00:00</t>
+    <t>2025-09-04T10:23:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -84,7 +84,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Cette entrée de type observation permet de décrire et de suivre le statut métier d’un objet.</t>
+    <t>FrObservationStatut permet de décrire et de suivre le statut métier d’un objet.</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -1377,7 +1377,10 @@
 </t>
   </si>
   <si>
-    <t>Qualifier du code</t>
+    <t>Extension - Qualifier du code</t>
+  </si>
+  <si>
+    <t>Extension permettant d’associer à un code une précision (qualifier).</t>
   </si>
   <si>
     <t>Observation.value[x].coding.extension:qualifier.id</t>
@@ -10179,7 +10182,7 @@
         <v>438</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>355</v>
+        <v>439</v>
       </c>
       <c r="N66" s="2"/>
       <c r="O66" s="2"/>
@@ -10265,10 +10268,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10383,10 +10386,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10501,13 +10504,13 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
+        <v>444</v>
+      </c>
+      <c r="B69" t="s" s="2">
         <v>443</v>
       </c>
-      <c r="B69" t="s" s="2">
-        <v>442</v>
-      </c>
       <c r="C69" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="D69" t="s" s="2">
         <v>82</v>
@@ -10621,10 +10624,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10739,10 +10742,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10857,10 +10860,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10900,7 +10903,7 @@
       </c>
       <c r="Q72" s="2"/>
       <c r="R72" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="S72" t="s" s="2">
         <v>82</v>
@@ -10977,10 +10980,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -11021,7 +11024,7 @@
         <v>82</v>
       </c>
       <c r="S73" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="T73" t="s" s="2">
         <v>82</v>
@@ -11095,10 +11098,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="C74" t="s" s="2">
         <v>428</v>
@@ -11215,10 +11218,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11333,10 +11336,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11451,10 +11454,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -11571,10 +11574,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11689,10 +11692,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11732,7 +11735,7 @@
       </c>
       <c r="Q79" s="2"/>
       <c r="R79" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="S79" t="s" s="2">
         <v>82</v>
@@ -11809,10 +11812,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -11927,10 +11930,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -12049,10 +12052,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -12169,10 +12172,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -12289,10 +12292,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -12409,10 +12412,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -12531,10 +12534,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -12653,10 +12656,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -12682,16 +12685,16 @@
         <v>192</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="N87" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="O87" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="P87" t="s" s="2">
         <v>82</v>
@@ -12719,10 +12722,10 @@
         <v>405</v>
       </c>
       <c r="Y87" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="Z87" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="AA87" t="s" s="2">
         <v>82</v>
@@ -12740,7 +12743,7 @@
         <v>82</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>80</v>
@@ -12749,7 +12752,7 @@
         <v>93</v>
       </c>
       <c r="AI87" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="AJ87" t="s" s="2">
         <v>105</v>
@@ -12764,7 +12767,7 @@
         <v>136</v>
       </c>
       <c r="AN87" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="AO87" t="s" s="2">
         <v>82</v>
@@ -12775,14 +12778,14 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="E88" s="2"/>
       <c r="F88" t="s" s="2">
@@ -12804,16 +12807,16 @@
         <v>192</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="N88" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="O88" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="P88" t="s" s="2">
         <v>82</v>
@@ -12842,7 +12845,7 @@
       </c>
       <c r="Y88" s="2"/>
       <c r="Z88" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="AA88" t="s" s="2">
         <v>82</v>
@@ -12860,7 +12863,7 @@
         <v>82</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>80</v>
@@ -12878,27 +12881,27 @@
         <v>82</v>
       </c>
       <c r="AL88" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="AM88" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="AN88" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="AO88" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP88" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -12921,19 +12924,19 @@
         <v>82</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="N89" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="O89" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="P89" t="s" s="2">
         <v>82</v>
@@ -12982,7 +12985,7 @@
         <v>82</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>80</v>
@@ -13003,10 +13006,10 @@
         <v>82</v>
       </c>
       <c r="AM89" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="AN89" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="AO89" t="s" s="2">
         <v>82</v>
@@ -13017,10 +13020,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -13046,13 +13049,13 @@
         <v>192</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="N90" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="O90" s="2"/>
       <c r="P90" t="s" s="2">
@@ -13081,10 +13084,10 @@
         <v>207</v>
       </c>
       <c r="Y90" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="Z90" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="AA90" t="s" s="2">
         <v>82</v>
@@ -13102,7 +13105,7 @@
         <v>82</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>80</v>
@@ -13120,27 +13123,27 @@
         <v>82</v>
       </c>
       <c r="AL90" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="AM90" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="AN90" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="AO90" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP90" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -13166,16 +13169,16 @@
         <v>192</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="N91" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="O91" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="P91" t="s" s="2">
         <v>82</v>
@@ -13204,7 +13207,7 @@
       </c>
       <c r="Y91" s="2"/>
       <c r="Z91" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="AA91" t="s" s="2">
         <v>82</v>
@@ -13222,7 +13225,7 @@
         <v>82</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>80</v>
@@ -13243,10 +13246,10 @@
         <v>82</v>
       </c>
       <c r="AM91" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="AN91" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="AO91" t="s" s="2">
         <v>82</v>
@@ -13257,10 +13260,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -13283,16 +13286,16 @@
         <v>82</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="N92" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="O92" s="2"/>
       <c r="P92" t="s" s="2">
@@ -13342,7 +13345,7 @@
         <v>82</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>80</v>
@@ -13360,27 +13363,27 @@
         <v>82</v>
       </c>
       <c r="AL92" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="AM92" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="AN92" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="AO92" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP92" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -13403,16 +13406,16 @@
         <v>82</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="N93" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="O93" s="2"/>
       <c r="P93" t="s" s="2">
@@ -13462,7 +13465,7 @@
         <v>82</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>80</v>
@@ -13480,27 +13483,27 @@
         <v>82</v>
       </c>
       <c r="AL93" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="AM93" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="AN93" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="AO93" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP93" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -13523,19 +13526,19 @@
         <v>82</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="N94" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="O94" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="P94" t="s" s="2">
         <v>82</v>
@@ -13584,7 +13587,7 @@
         <v>82</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>80</v>
@@ -13596,7 +13599,7 @@
         <v>82</v>
       </c>
       <c r="AJ94" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="AK94" t="s" s="2">
         <v>82</v>
@@ -13605,10 +13608,10 @@
         <v>82</v>
       </c>
       <c r="AM94" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="AN94" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="AO94" t="s" s="2">
         <v>82</v>
@@ -13619,10 +13622,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -13737,10 +13740,10 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -13857,14 +13860,14 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="E97" s="2"/>
       <c r="F97" t="s" s="2">
@@ -13886,10 +13889,10 @@
         <v>139</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="N97" t="s" s="2">
         <v>142</v>
@@ -13944,7 +13947,7 @@
         <v>82</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>80</v>
@@ -13979,10 +13982,10 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -14005,13 +14008,13 @@
         <v>82</v>
       </c>
       <c r="K98" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="N98" s="2"/>
       <c r="O98" s="2"/>
@@ -14062,7 +14065,7 @@
         <v>82</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>80</v>
@@ -14071,7 +14074,7 @@
         <v>93</v>
       </c>
       <c r="AI98" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="AJ98" t="s" s="2">
         <v>105</v>
@@ -14083,10 +14086,10 @@
         <v>82</v>
       </c>
       <c r="AM98" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="AN98" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="AO98" t="s" s="2">
         <v>82</v>
@@ -14097,10 +14100,10 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -14123,13 +14126,13 @@
         <v>82</v>
       </c>
       <c r="K99" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="N99" s="2"/>
       <c r="O99" s="2"/>
@@ -14180,7 +14183,7 @@
         <v>82</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>80</v>
@@ -14189,7 +14192,7 @@
         <v>93</v>
       </c>
       <c r="AI99" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="AJ99" t="s" s="2">
         <v>105</v>
@@ -14201,10 +14204,10 @@
         <v>82</v>
       </c>
       <c r="AM99" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="AN99" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="AO99" t="s" s="2">
         <v>82</v>
@@ -14215,10 +14218,10 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -14244,16 +14247,16 @@
         <v>192</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="N100" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="O100" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="P100" t="s" s="2">
         <v>82</v>
@@ -14281,10 +14284,10 @@
         <v>117</v>
       </c>
       <c r="Y100" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="Z100" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="AA100" t="s" s="2">
         <v>82</v>
@@ -14302,7 +14305,7 @@
         <v>82</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>80</v>
@@ -14320,13 +14323,13 @@
         <v>82</v>
       </c>
       <c r="AL100" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="AM100" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="AN100" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="AO100" t="s" s="2">
         <v>82</v>
@@ -14337,10 +14340,10 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -14366,16 +14369,16 @@
         <v>192</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="N101" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="O101" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="P101" t="s" s="2">
         <v>82</v>
@@ -14403,10 +14406,10 @@
         <v>207</v>
       </c>
       <c r="Y101" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="Z101" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="AA101" t="s" s="2">
         <v>82</v>
@@ -14424,7 +14427,7 @@
         <v>82</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>80</v>
@@ -14442,13 +14445,13 @@
         <v>82</v>
       </c>
       <c r="AL101" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="AM101" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="AN101" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="AO101" t="s" s="2">
         <v>82</v>
@@ -14459,10 +14462,10 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -14485,17 +14488,17 @@
         <v>82</v>
       </c>
       <c r="K102" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="N102" s="2"/>
       <c r="O102" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="P102" t="s" s="2">
         <v>82</v>
@@ -14544,7 +14547,7 @@
         <v>82</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>80</v>
@@ -14568,7 +14571,7 @@
         <v>82</v>
       </c>
       <c r="AN102" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="AO102" t="s" s="2">
         <v>82</v>
@@ -14579,10 +14582,10 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -14608,10 +14611,10 @@
         <v>217</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="N103" s="2"/>
       <c r="O103" s="2"/>
@@ -14662,7 +14665,7 @@
         <v>82</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>80</v>
@@ -14683,10 +14686,10 @@
         <v>82</v>
       </c>
       <c r="AM103" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="AN103" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="AO103" t="s" s="2">
         <v>82</v>
@@ -14697,10 +14700,10 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -14723,16 +14726,16 @@
         <v>94</v>
       </c>
       <c r="K104" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="N104" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="O104" s="2"/>
       <c r="P104" t="s" s="2">
@@ -14782,7 +14785,7 @@
         <v>82</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>80</v>
@@ -14803,10 +14806,10 @@
         <v>82</v>
       </c>
       <c r="AM104" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="AN104" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="AO104" t="s" s="2">
         <v>82</v>
@@ -14817,10 +14820,10 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -14843,16 +14846,16 @@
         <v>94</v>
       </c>
       <c r="K105" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="N105" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="O105" s="2"/>
       <c r="P105" t="s" s="2">
@@ -14902,7 +14905,7 @@
         <v>82</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>80</v>
@@ -14923,10 +14926,10 @@
         <v>82</v>
       </c>
       <c r="AM105" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="AN105" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="AO105" t="s" s="2">
         <v>82</v>
@@ -14937,10 +14940,10 @@
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -14963,19 +14966,19 @@
         <v>94</v>
       </c>
       <c r="K106" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="N106" t="s" s="2">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="O106" t="s" s="2">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="P106" t="s" s="2">
         <v>82</v>
@@ -15024,7 +15027,7 @@
         <v>82</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>80</v>
@@ -15045,10 +15048,10 @@
         <v>82</v>
       </c>
       <c r="AM106" t="s" s="2">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="AN106" t="s" s="2">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="AO106" t="s" s="2">
         <v>82</v>
@@ -15059,10 +15062,10 @@
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -15177,10 +15180,10 @@
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -15297,14 +15300,14 @@
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="E109" s="2"/>
       <c r="F109" t="s" s="2">
@@ -15326,10 +15329,10 @@
         <v>139</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="N109" t="s" s="2">
         <v>142</v>
@@ -15384,7 +15387,7 @@
         <v>82</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>80</v>
@@ -15419,10 +15422,10 @@
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -15448,13 +15451,13 @@
         <v>192</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="M110" t="s" s="2">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="N110" t="s" s="2">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="O110" t="s" s="2">
         <v>206</v>
@@ -15506,7 +15509,7 @@
         <v>82</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>93</v>
@@ -15524,7 +15527,7 @@
         <v>82</v>
       </c>
       <c r="AL110" t="s" s="2">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="AM110" t="s" s="2">
         <v>212</v>
@@ -15541,10 +15544,10 @@
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -15567,16 +15570,16 @@
         <v>94</v>
       </c>
       <c r="K111" t="s" s="2">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="M111" t="s" s="2">
         <v>422</v>
       </c>
       <c r="N111" t="s" s="2">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="O111" t="s" s="2">
         <v>424</v>
@@ -15628,7 +15631,7 @@
         <v>82</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>80</v>
@@ -15646,7 +15649,7 @@
         <v>82</v>
       </c>
       <c r="AL111" t="s" s="2">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="AM111" t="s" s="2">
         <v>427</v>
@@ -15663,10 +15666,10 @@
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -15692,16 +15695,16 @@
         <v>192</v>
       </c>
       <c r="L112" t="s" s="2">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="M112" t="s" s="2">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="N112" t="s" s="2">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="O112" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="P112" t="s" s="2">
         <v>82</v>
@@ -15729,10 +15732,10 @@
         <v>405</v>
       </c>
       <c r="Y112" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="Z112" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="AA112" t="s" s="2">
         <v>82</v>
@@ -15750,7 +15753,7 @@
         <v>82</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>80</v>
@@ -15759,7 +15762,7 @@
         <v>93</v>
       </c>
       <c r="AI112" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="AJ112" t="s" s="2">
         <v>105</v>
@@ -15774,7 +15777,7 @@
         <v>136</v>
       </c>
       <c r="AN112" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="AO112" t="s" s="2">
         <v>82</v>
@@ -15785,14 +15788,14 @@
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="E113" s="2"/>
       <c r="F113" t="s" s="2">
@@ -15814,16 +15817,16 @@
         <v>192</v>
       </c>
       <c r="L113" t="s" s="2">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="M113" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="N113" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="O113" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="P113" t="s" s="2">
         <v>82</v>
@@ -15851,10 +15854,10 @@
         <v>405</v>
       </c>
       <c r="Y113" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="Z113" t="s" s="2">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="AA113" t="s" s="2">
         <v>82</v>
@@ -15872,7 +15875,7 @@
         <v>82</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>80</v>
@@ -15890,27 +15893,27 @@
         <v>82</v>
       </c>
       <c r="AL113" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="AM113" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="AN113" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="AO113" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP113" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -15936,16 +15939,16 @@
         <v>83</v>
       </c>
       <c r="L114" t="s" s="2">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="M114" t="s" s="2">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="N114" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="O114" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="P114" t="s" s="2">
         <v>82</v>
@@ -15994,7 +15997,7 @@
         <v>82</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>80</v>
@@ -16015,10 +16018,10 @@
         <v>82</v>
       </c>
       <c r="AM114" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="AN114" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="AO114" t="s" s="2">
         <v>82</v>
